--- a/artfynd/A 55598-2025 artfynd.xlsx
+++ b/artfynd/A 55598-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118184</v>
       </c>
       <c r="B2" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55598-2025 artfynd.xlsx
+++ b/artfynd/A 55598-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118184</v>
       </c>
       <c r="B2" t="n">
-        <v>91806</v>
+        <v>91809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55598-2025 artfynd.xlsx
+++ b/artfynd/A 55598-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118184</v>
       </c>
       <c r="B2" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55598-2025 artfynd.xlsx
+++ b/artfynd/A 55598-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118184</v>
       </c>
       <c r="B2" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55598-2025 artfynd.xlsx
+++ b/artfynd/A 55598-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118184</v>
       </c>
       <c r="B2" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55598-2025 artfynd.xlsx
+++ b/artfynd/A 55598-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118184</v>
       </c>
       <c r="B2" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55598-2025 artfynd.xlsx
+++ b/artfynd/A 55598-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118184</v>
       </c>
       <c r="B2" t="n">
-        <v>91814</v>
+        <v>91817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55598-2025 artfynd.xlsx
+++ b/artfynd/A 55598-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118184</v>
       </c>
       <c r="B2" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55598-2025 artfynd.xlsx
+++ b/artfynd/A 55598-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118184</v>
       </c>
       <c r="B2" t="n">
-        <v>91818</v>
+        <v>91824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55598-2025 artfynd.xlsx
+++ b/artfynd/A 55598-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118184</v>
       </c>
       <c r="B2" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55598-2025 artfynd.xlsx
+++ b/artfynd/A 55598-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118184</v>
       </c>
       <c r="B2" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55598-2025 artfynd.xlsx
+++ b/artfynd/A 55598-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118184</v>
       </c>
       <c r="B2" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
